--- a/artfynd/A 53436-2023 artfynd.xlsx
+++ b/artfynd/A 53436-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53436-2023 artfynd.xlsx
+++ b/artfynd/A 53436-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114359103</v>
+        <v>114359097</v>
       </c>
       <c r="B2" t="n">
-        <v>100812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627021</v>
+        <v>627269</v>
       </c>
       <c r="R2" t="n">
-        <v>6937947</v>
+        <v>6938012</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -780,12 +775,7 @@
         <v>114359098</v>
       </c>
       <c r="B3" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114359106</v>
+        <v>114359102</v>
       </c>
       <c r="B4" t="n">
-        <v>96822</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220250</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627054</v>
+        <v>627143</v>
       </c>
       <c r="R4" t="n">
-        <v>6938028</v>
+        <v>6938027</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114359104</v>
+        <v>114359101</v>
       </c>
       <c r="B5" t="n">
-        <v>96822</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220250</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627027</v>
+        <v>627180</v>
       </c>
       <c r="R5" t="n">
-        <v>6937971</v>
+        <v>6938045</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114359097</v>
+        <v>114359104</v>
       </c>
       <c r="B6" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627269</v>
+        <v>627027</v>
       </c>
       <c r="R6" t="n">
-        <v>6938012</v>
+        <v>6937971</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114359105</v>
+        <v>114359106</v>
       </c>
       <c r="B7" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,43 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220250</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Edsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627033</v>
+        <v>627054</v>
       </c>
       <c r="R7" t="n">
-        <v>6937995</v>
+        <v>6938028</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1272,11 +1233,6 @@
           <t>2023-06-03</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>30x80 cm</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1298,6 +1254,214 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114359103</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Edsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>627021</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6937947</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-06-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-06-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114359105</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Edsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>627033</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6937995</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-06-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-06-03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>30x80 cm</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53436-2023 artfynd.xlsx
+++ b/artfynd/A 53436-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359097</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359098</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359102</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359101</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359104</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359106</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359103</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1462,8 +1502,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359105</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>